--- a/Grondwatergebruiksysteem (GUF)/BROObject - GUF pumping well datafile NL (v0.61).xlsx
+++ b/Grondwatergebruiksysteem (GUF)/BROObject - GUF pumping well datafile NL (v0.61).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://3hydro-my.sharepoint.com/personal/jos_von_asmuth_3hydro_nl/Documents/MATLAB/Menyanthes/DocumentenSVN/Data/BRO-Spreadsheet-en-tabelformat/Grondwatergebruiksysteem (GUF)/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://3hydro-my.sharepoint.com/personal/jos_von_asmuth_3hydro_nl/Documents/GitHub/QC-Protocol/BRO-Spreadsheet-en-tabelformat/Grondwatergebruiksysteem (GUF)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="193" documentId="14_{1F356C3A-F176-4ED0-B40C-E4D1DE1395FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C34C9D86-6393-426D-80A2-064D4667B3E9}"/>
+  <xr:revisionPtr revIDLastSave="195" documentId="14_{1F356C3A-F176-4ED0-B40C-E4D1DE1395FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37BC6AF5-9462-4D38-A388-CF2127F009DA}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{26814B37-6F38-4D5A-99CF-A0A5CD7480CB}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{26814B37-6F38-4D5A-99CF-A0A5CD7480CB}"/>
   </bookViews>
   <sheets>
     <sheet name="Toelichting" sheetId="8" r:id="rId1"/>
@@ -1258,10 +1258,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
